--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Game/CellEffect.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Game/CellEffect.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nevoa</t>
+          <t>Névoa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
